--- a/BWI/bestwine_output/bestwine_Jamaica.xlsx
+++ b/BWI/bestwine_output/bestwine_Jamaica.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA24"/>
+  <dimension ref="A1:AA25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3098,6 +3098,99 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Dufry Jamaica Limited</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Dufry Jamaica Limited</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>89113</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Montego Bay</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>St. James Parish</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Alice Eldemire Drive</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>https://jamaica.shopdutyfree.com, https://jamaica.shopdutyfree.comen103</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>customerservices.jm@wdfg.com</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>+1 876-979-2331</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>80174</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>Tajay Gordon</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>Sales Associate</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tajay-gordon-369616195</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Jamaica.xlsx
+++ b/BWI/bestwine_output/bestwine_Jamaica.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA25"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3191,6 +3191,95 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Mandeville Liquor Store Limited</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Mandeville Liquor Store Limited</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>141291</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Mandeville</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Manchester Parish</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>4 Villa Road</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://mandevilleliquorstore.com</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>info@mandevilleliquorstore.com</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>+1 876-625-6900</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>73637</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mandeville-liquor-store/</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mandevilleliquorstore</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr"/>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
